--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -58,7 +58,7 @@
     <t/>
   </si>
   <si>
-    <t>대기</t>
+    <t>완료</t>
   </si>
   <si>
     <t>22~26년</t>
@@ -679,7 +679,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>대기</t>
+    <t>완료</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -777,7 +777,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>대기</t>
+    <t>완료</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
